--- a/游戏设计王/老虎机数学专题-超级堆叠.xlsx
+++ b/游戏设计王/老虎机数学专题-超级堆叠.xlsx
@@ -561,12 +561,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
+    <numFmt numFmtId="177" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1272,7 +1273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1363,6 +1364,10 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -9770,7 +9775,7 @@
       <c r="C93" s="4">
         <v>5</v>
       </c>
-      <c r="D93" s="13">
+      <c r="D93" s="48">
         <f>B93*D83/POWER(40,5)</f>
         <v>0.02953125</v>
       </c>
@@ -9807,7 +9812,7 @@
       <c r="C94" s="4">
         <v>4</v>
       </c>
-      <c r="D94" s="13">
+      <c r="D94" s="48">
         <f>B94*C83/POWER(40,5)</f>
         <v>0.030515625</v>
       </c>
@@ -9844,7 +9849,7 @@
       <c r="C95" s="4">
         <v>3</v>
       </c>
-      <c r="D95" s="13">
+      <c r="D95" s="48">
         <f>B95*B83/POWER(40,5)</f>
         <v>0.02625</v>
       </c>
@@ -9881,7 +9886,7 @@
       <c r="C96" s="4">
         <v>5</v>
       </c>
-      <c r="D96" s="13">
+      <c r="D96" s="48">
         <f>B96*D84/POWER(40,5)</f>
         <v>0.02953125</v>
       </c>
@@ -9918,7 +9923,7 @@
       <c r="C97" s="4">
         <v>4</v>
       </c>
-      <c r="D97" s="13">
+      <c r="D97" s="48">
         <f>B97*C84/POWER(40,5)</f>
         <v>0.02953125</v>
       </c>
@@ -9955,7 +9960,7 @@
       <c r="C98" s="4">
         <v>3</v>
       </c>
-      <c r="D98" s="13">
+      <c r="D98" s="48">
         <f>B98*B84/POWER(40,5)</f>
         <v>0.0348046875</v>
       </c>
@@ -9992,7 +9997,7 @@
       <c r="C99" s="4">
         <v>5</v>
       </c>
-      <c r="D99" s="13">
+      <c r="D99" s="48">
         <f>B99*D85/POWER(40,5)</f>
         <v>0.0221484375</v>
       </c>
@@ -10029,7 +10034,7 @@
       <c r="C100" s="4">
         <v>4</v>
       </c>
-      <c r="D100" s="13">
+      <c r="D100" s="48">
         <f>B100*C85/POWER(40,5)</f>
         <v>0.02784375</v>
       </c>
@@ -10066,7 +10071,7 @@
       <c r="C101" s="4">
         <v>3</v>
       </c>
-      <c r="D101" s="13">
+      <c r="D101" s="48">
         <f>B101*B85/POWER(40,5)</f>
         <v>0.0478125</v>
       </c>
@@ -10103,7 +10108,7 @@
       <c r="C102" s="4">
         <v>5</v>
       </c>
-      <c r="D102" s="13">
+      <c r="D102" s="48">
         <f>B102*D86/POWER(40,5)</f>
         <v>0.0221484375</v>
       </c>
@@ -10140,7 +10145,7 @@
       <c r="C103" s="4">
         <v>4</v>
       </c>
-      <c r="D103" s="13">
+      <c r="D103" s="48">
         <f>B103*C86/POWER(40,5)</f>
         <v>0.03346875</v>
       </c>
@@ -10177,7 +10182,7 @@
       <c r="C104" s="4">
         <v>3</v>
       </c>
-      <c r="D104" s="13">
+      <c r="D104" s="48">
         <f>B104*B86/POWER(40,5)</f>
         <v>0.02953125</v>
       </c>
@@ -10214,7 +10219,7 @@
       <c r="C105" s="4">
         <v>5</v>
       </c>
-      <c r="D105" s="13">
+      <c r="D105" s="48">
         <f>B105*D87/POWER(40,5)</f>
         <v>0.014765625</v>
       </c>
@@ -10251,7 +10256,7 @@
       <c r="C106" s="4">
         <v>4</v>
       </c>
-      <c r="D106" s="13">
+      <c r="D106" s="48">
         <f>B106*C87/POWER(40,5)</f>
         <v>0.008859375</v>
       </c>
@@ -10288,7 +10293,7 @@
       <c r="C107" s="4">
         <v>3</v>
       </c>
-      <c r="D107" s="13">
+      <c r="D107" s="48">
         <f>B107*B87/POWER(40,5)</f>
         <v>0.02034375</v>
       </c>
@@ -10324,7 +10329,7 @@
       <c r="C108" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D108" s="16">
+      <c r="D108" s="50">
         <f>SUM(D93:D107)</f>
         <v>0.4070859375</v>
       </c>
